--- a/20250413_NCOPS/03_document/instruction.xlsx
+++ b/20250413_NCOPS/03_document/instruction.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Professional\04_Git\AI_Power_Studio\20250413_NCOPS\03_document\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5110B5A5-A1DB-43BA-90DC-55C881F4A2E9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13813B3A-2E8E-481C-B8BA-91DE1B7DD030}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21360" xr2:uid="{6E468DB2-7AAC-45EB-A7F3-D82F663708E0}"/>
+    <workbookView xWindow="5530" yWindow="930" windowWidth="28300" windowHeight="20370" xr2:uid="{6E468DB2-7AAC-45EB-A7F3-D82F663708E0}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -272,7 +272,7 @@
     <numFmt numFmtId="176" formatCode="_(* #,##0.00_);_(* \(#,##0.00\);_(* &quot;-&quot;??_);_(@_)"/>
     <numFmt numFmtId="177" formatCode="_-* #,##0.0_-;\-* #,##0.0_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -333,12 +333,6 @@
       <family val="2"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <b/>
       <sz val="10"/>
       <name val="等线"/>
@@ -360,7 +354,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="10">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -409,8 +403,14 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -444,6 +444,112 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -452,7 +558,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
@@ -486,13 +592,27 @@
     <xf numFmtId="16" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="177" fontId="10" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="177" fontId="9" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="百分比" xfId="2" builtinId="5"/>
@@ -523,7 +643,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>1060450</xdr:colOff>
+      <xdr:colOff>187325</xdr:colOff>
       <xdr:row>22</xdr:row>
       <xdr:rowOff>41723</xdr:rowOff>
     </xdr:to>
@@ -560,16 +680,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>457200</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>183356</xdr:colOff>
       <xdr:row>59</xdr:row>
-      <xdr:rowOff>76200</xdr:rowOff>
+      <xdr:rowOff>48419</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>476376</xdr:colOff>
+      <xdr:colOff>1520157</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>63509</xdr:rowOff>
+      <xdr:rowOff>35728</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -592,8 +712,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3505200" y="10941050"/>
-          <a:ext cx="2457576" cy="171459"/>
+          <a:off x="5426075" y="10585450"/>
+          <a:ext cx="2654426" cy="165903"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -604,16 +724,16 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>5</xdr:col>
-      <xdr:colOff>469900</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>6350</xdr:rowOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>168274</xdr:colOff>
+      <xdr:row>60</xdr:row>
+      <xdr:rowOff>153195</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>9</xdr:col>
-      <xdr:colOff>927249</xdr:colOff>
+      <xdr:colOff>1943248</xdr:colOff>
       <xdr:row>62</xdr:row>
-      <xdr:rowOff>50812</xdr:rowOff>
+      <xdr:rowOff>15095</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -636,8 +756,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="3517900" y="11239500"/>
-          <a:ext cx="2895749" cy="228612"/>
+          <a:off x="5410993" y="10868820"/>
+          <a:ext cx="3092599" cy="223056"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -699,7 +819,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>425529</xdr:colOff>
+      <xdr:colOff>183435</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>57169</xdr:rowOff>
     </xdr:to>
@@ -806,6 +926,61 @@
         </a:extLst>
       </xdr:spPr>
     </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>15876</xdr:colOff>
+      <xdr:row>64</xdr:row>
+      <xdr:rowOff>75405</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>154783</xdr:colOff>
+      <xdr:row>70</xdr:row>
+      <xdr:rowOff>146842</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="9" name="连接符: 曲线 8">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{AAA53FD6-7C7E-7B6C-9982-CB45098EF44B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="16200000" flipH="1">
+          <a:off x="4510485" y="11594702"/>
+          <a:ext cx="1635125" cy="1456532"/>
+        </a:xfrm>
+        <a:prstGeom prst="curvedConnector3">
+          <a:avLst>
+            <a:gd name="adj1" fmla="val -5340"/>
+          </a:avLst>
+        </a:prstGeom>
+        <a:ln>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1108,9 +1283,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{688EF363-D35A-4F11-B72F-2D7024E28D50}">
-  <dimension ref="A2:S83"/>
+  <dimension ref="A2:S84"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
+    <col min="1" max="1" width="16.9140625" customWidth="1"/>
+    <col min="6" max="6" width="11.83203125" customWidth="1"/>
     <col min="10" max="10" width="31.1640625" customWidth="1"/>
     <col min="11" max="11" width="27.33203125" customWidth="1"/>
     <col min="12" max="13" width="5.08203125" customWidth="1"/>
@@ -1134,7 +1311,7 @@
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="J50" s="17">
+      <c r="J50" s="16">
         <f>(66-55)/55</f>
         <v>0.2</v>
       </c>
@@ -1143,7 +1320,7 @@
       <c r="A51" t="s">
         <v>3</v>
       </c>
-      <c r="J51" s="17">
+      <c r="J51" s="16">
         <f>(7-62)/62</f>
         <v>-0.88709677419354838</v>
       </c>
@@ -1157,7 +1334,7 @@
       <c r="A53" t="s">
         <v>5</v>
       </c>
-      <c r="J53" s="17">
+      <c r="J53" s="16">
         <f>(8-7)/7</f>
         <v>0.14285714285714285</v>
       </c>
@@ -1233,20 +1410,21 @@
       <c r="H59" s="3"/>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="K60" s="17">
+      <c r="K60" s="16">
         <f>(476-536)/536</f>
         <v>-0.11194029850746269</v>
       </c>
     </row>
+    <row r="61" spans="1:11" ht="14.5" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="62" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A62" s="7" t="s">
+      <c r="A62" s="18" t="s">
         <v>12</v>
       </c>
-      <c r="B62" s="7"/>
-      <c r="C62" s="7"/>
-      <c r="D62" s="7"/>
-      <c r="E62" s="7"/>
-      <c r="F62" s="7"/>
+      <c r="B62" s="19"/>
+      <c r="C62" s="19"/>
+      <c r="D62" s="19"/>
+      <c r="E62" s="19"/>
+      <c r="F62" s="20"/>
       <c r="G62" s="7"/>
       <c r="H62" s="7"/>
       <c r="I62" s="7"/>
@@ -1254,14 +1432,14 @@
       <c r="K62" s="7"/>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A63" s="7" t="s">
+      <c r="A63" s="21" t="s">
         <v>11</v>
       </c>
-      <c r="B63" s="7"/>
-      <c r="C63" s="7"/>
-      <c r="D63" s="7"/>
-      <c r="E63" s="7"/>
-      <c r="F63" s="7"/>
+      <c r="B63" s="22"/>
+      <c r="C63" s="22"/>
+      <c r="D63" s="22"/>
+      <c r="E63" s="22"/>
+      <c r="F63" s="23"/>
       <c r="G63" s="7"/>
       <c r="H63" s="7"/>
       <c r="I63" s="7"/>
@@ -1269,14 +1447,14 @@
       <c r="K63" s="7"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.3">
-      <c r="A64" s="7" t="s">
+      <c r="A64" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="B64" s="7"/>
-      <c r="C64" s="7"/>
-      <c r="D64" s="7"/>
-      <c r="E64" s="7"/>
-      <c r="F64" s="7"/>
+      <c r="B64" s="22"/>
+      <c r="C64" s="22"/>
+      <c r="D64" s="22"/>
+      <c r="E64" s="22"/>
+      <c r="F64" s="23"/>
       <c r="G64" s="7"/>
       <c r="H64" s="7"/>
       <c r="I64" s="7"/>
@@ -1284,218 +1462,233 @@
       <c r="K64" s="7"/>
     </row>
     <row r="65" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A65" s="7" t="s">
+      <c r="A65" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="B65" s="7"/>
-      <c r="C65" s="7"/>
-      <c r="D65" s="7"/>
-      <c r="E65" s="7"/>
-      <c r="F65" s="7"/>
-    </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="A66" s="7" t="s">
+      <c r="B65" s="22"/>
+      <c r="C65" s="22"/>
+      <c r="D65" s="22"/>
+      <c r="E65" s="22"/>
+      <c r="F65" s="23"/>
+    </row>
+    <row r="66" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A66" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="B66" s="7"/>
-      <c r="C66" s="7"/>
-      <c r="D66" s="7"/>
-      <c r="E66" s="7"/>
-      <c r="F66" s="7"/>
-    </row>
-    <row r="67" spans="1:18" ht="53.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A67" s="7" t="s">
+      <c r="B66" s="26"/>
+      <c r="C66" s="26"/>
+      <c r="D66" s="26"/>
+      <c r="E66" s="26"/>
+      <c r="F66" s="27"/>
+    </row>
+    <row r="67" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A67" s="25"/>
+      <c r="B67" s="26"/>
+      <c r="C67" s="22"/>
+      <c r="D67" s="22"/>
+      <c r="E67" s="22"/>
+      <c r="F67" s="22"/>
+    </row>
+    <row r="68" spans="1:18" ht="53.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A68" s="28" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
-      <c r="G68" s="7"/>
-      <c r="H68" s="7"/>
-      <c r="I68" s="7"/>
-      <c r="J68" s="7" t="s">
+      <c r="B68" s="29"/>
+    </row>
+    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+      <c r="G69" s="7"/>
+      <c r="H69" s="7"/>
+      <c r="I69" s="7"/>
+      <c r="J69" s="7" t="s">
         <v>15</v>
       </c>
-      <c r="K68" s="7"/>
-    </row>
-    <row r="69" spans="1:18" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G69" s="8" t="s">
+      <c r="K69" s="7"/>
+    </row>
+    <row r="70" spans="1:18" ht="27.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G70" s="8" t="s">
         <v>19</v>
       </c>
-      <c r="H69" s="8" t="s">
+      <c r="H70" s="8" t="s">
         <v>14</v>
       </c>
-      <c r="I69" s="8" t="s">
+      <c r="I70" s="8" t="s">
         <v>18</v>
       </c>
-      <c r="J69" s="9" t="s">
+      <c r="J70" s="9" t="s">
         <v>24</v>
       </c>
-      <c r="K69" s="9" t="s">
+      <c r="K70" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="N69" s="11" t="s">
+      <c r="N70" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="O69" s="11" t="s">
+      <c r="O70" s="11" t="s">
         <v>44</v>
       </c>
-      <c r="P69" s="11"/>
-      <c r="R69" s="11"/>
-    </row>
-    <row r="70" spans="1:18" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G70" s="6" t="s">
+      <c r="P70" s="11"/>
+      <c r="R70" s="11"/>
+    </row>
+    <row r="71" spans="1:18" ht="46" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G71" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="H70" s="5" t="s">
+      <c r="H71" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="I70" s="5" t="s">
+      <c r="I71" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="J70" s="11" t="s">
+      <c r="J71" s="11" t="s">
         <v>51</v>
       </c>
-      <c r="K70" s="11" t="s">
+      <c r="K71" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="N70" s="8" t="s">
+      <c r="N71" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="O70" s="8" t="s">
+      <c r="O71" s="8" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="71" spans="1:18" ht="16" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="F71" s="10"/>
-      <c r="N71" s="4" t="s">
+    <row r="72" spans="1:18" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="F72" s="10"/>
+      <c r="I72" s="17">
+        <v>45748</v>
+      </c>
+      <c r="N72" s="4" t="s">
         <v>25</v>
       </c>
-      <c r="O71" s="15" t="s">
+      <c r="O72" s="4" t="s">
         <v>47</v>
       </c>
     </row>
-    <row r="72" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G72" s="8" t="s">
+    <row r="73" spans="1:18" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G73" s="8" t="s">
         <v>26</v>
       </c>
-      <c r="H72" s="8" t="s">
+      <c r="H73" s="8" t="s">
         <v>27</v>
       </c>
     </row>
-    <row r="73" spans="1:18" ht="40" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G73" s="12" t="s">
+    <row r="74" spans="1:18" ht="40" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G74" s="12" t="s">
         <v>25</v>
       </c>
-      <c r="H73" s="5" t="s">
+      <c r="H74" s="5" t="s">
         <v>28</v>
       </c>
-      <c r="J73" t="s">
+      <c r="J74" t="s">
         <v>46</v>
       </c>
-      <c r="N73" s="8" t="s">
+      <c r="N74" s="8" t="s">
         <v>27</v>
       </c>
-      <c r="O73" s="8" t="s">
+      <c r="O74" s="8" t="s">
         <v>48</v>
       </c>
     </row>
-    <row r="74" spans="1:18" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="N74" s="16" t="s">
+    <row r="75" spans="1:18" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="N75" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="O74" s="16" t="s">
+      <c r="O75" s="15" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="81" spans="7:19" x14ac:dyDescent="0.3">
-      <c r="G81" t="s">
+    <row r="82" spans="7:19" x14ac:dyDescent="0.3">
+      <c r="G82" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="82" spans="7:19" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="G82" s="8" t="s">
+    <row r="83" spans="7:19" ht="14.5" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="G83" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="H82" t="s">
+      <c r="H83" t="s">
         <v>33</v>
       </c>
-      <c r="I82" t="s">
+      <c r="I83" t="s">
         <v>9</v>
       </c>
-      <c r="J82" t="s">
+      <c r="J83" t="s">
         <v>10</v>
       </c>
-      <c r="K82" t="s">
+      <c r="K83" t="s">
         <v>34</v>
       </c>
-      <c r="L82" t="s">
+      <c r="L83" t="s">
         <v>35</v>
       </c>
-      <c r="M82" t="s">
+      <c r="M83" t="s">
         <v>36</v>
       </c>
-      <c r="N82" t="s">
+      <c r="N83" t="s">
         <v>37</v>
       </c>
-      <c r="O82" t="s">
+      <c r="O83" t="s">
         <v>38</v>
       </c>
-      <c r="P82" t="s">
+      <c r="P83" t="s">
         <v>39</v>
       </c>
-      <c r="Q82" t="s">
+      <c r="Q83" t="s">
         <v>40</v>
       </c>
-      <c r="R82" t="s">
+      <c r="R83" t="s">
         <v>41</v>
       </c>
-      <c r="S82" t="s">
+      <c r="S83" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="83" spans="7:19" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="G83" s="13" t="s">
+    <row r="84" spans="7:19" ht="14.5" thickTop="1" x14ac:dyDescent="0.3">
+      <c r="G84" s="13" t="s">
         <v>32</v>
       </c>
-      <c r="H83" s="14">
+      <c r="H84" s="14">
         <v>45682</v>
       </c>
-      <c r="I83" s="14">
+      <c r="I84" s="14">
         <v>45713</v>
       </c>
-      <c r="J83" s="14">
+      <c r="J84" s="14">
         <v>45741</v>
       </c>
-      <c r="K83" s="14">
+      <c r="K84" s="14">
         <v>45772</v>
       </c>
-      <c r="L83" s="14">
+      <c r="L84" s="14">
         <v>45802</v>
       </c>
-      <c r="M83" s="14">
+      <c r="M84" s="14">
         <v>45833</v>
       </c>
-      <c r="N83" s="14">
+      <c r="N84" s="14">
         <v>45863</v>
       </c>
-      <c r="O83" s="14">
+      <c r="O84" s="14">
         <v>45894</v>
       </c>
-      <c r="P83" s="14">
+      <c r="P84" s="14">
         <v>45925</v>
       </c>
-      <c r="Q83" s="14">
+      <c r="Q84" s="14">
         <v>45955</v>
       </c>
-      <c r="R83" s="14">
+      <c r="R84" s="14">
         <v>45986</v>
       </c>
-      <c r="S83" s="14">
+      <c r="S84" s="14">
         <v>46016</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <mergeCells count="1">
+    <mergeCell ref="A68:B68"/>
+  </mergeCells>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="360" verticalDpi="360" r:id="rId1"/>
   <drawing r:id="rId2"/>
